--- a/Loan MTM Source Evidence_calculation_test.xlsx
+++ b/Loan MTM Source Evidence_calculation_test.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Loan Activity Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ground Truth (Dev Only)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1073,505 +1072,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Sample</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>SourceRefID</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Shares</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Local Market Price</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>FX Rate to USD</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Correct MTM (USD)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Reported MTM (USD)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Variance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Error Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>LOAN-C001</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9162</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>91620</v>
-      </c>
-      <c r="H2" t="n">
-        <v>91620</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>LOAN-C002</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.124822</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>224964.4</v>
-      </c>
-      <c r="H3" t="n">
-        <v>224964.4</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LOAN-C003</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.072779</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>268194.75</v>
-      </c>
-      <c r="H4" t="n">
-        <v>268194.75</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LOAN-C004</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>500000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.029237</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>514618.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>514618.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LOAN-C005</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>125000</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.764072</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>95509</v>
-      </c>
-      <c r="H6" t="n">
-        <v>119386.25</v>
-      </c>
-      <c r="I6" t="n">
-        <v>23877.25</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Stale/wrong price used — reported MTM overstated by ~25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LOAN-C006</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.866805</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>173361</v>
-      </c>
-      <c r="H7" t="n">
-        <v>200000</v>
-      </c>
-      <c r="I7" t="n">
-        <v>26639</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Wrong notional applied — reported MTM overstated by ~26,639</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LOAN-C007</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="G8" t="n">
-        <v>102600</v>
-      </c>
-      <c r="H8" t="n">
-        <v>102600</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LOAN-C008</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>226800</v>
-      </c>
-      <c r="H9" t="n">
-        <v>226800</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>LOAN-C009</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>150000</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="G10" t="n">
-        <v>142560</v>
-      </c>
-      <c r="H10" t="n">
-        <v>132000</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-10560</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>FX conversion omitted — reporter used local EUR amount as USD directly</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>LOAN-C010</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="G11" t="n">
-        <v>124200</v>
-      </c>
-      <c r="H11" t="n">
-        <v>115000</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-9200</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>FX conversion omitted — reporter used local EUR amount as USD directly</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>